--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -2744,11 +2744,11 @@
         <v>119010671</v>
       </c>
       <c r="B22" t="n">
-        <v>57487</v>
+        <v>57657</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rapport ska skrivas (för Rrk)</t>
+          <t>Rapport skriven (för Rrk)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -2744,7 +2744,7 @@
         <v>119010671</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -2744,11 +2744,11 @@
         <v>119010671</v>
       </c>
       <c r="B22" t="n">
-        <v>57660</v>
+        <v>57666</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rapport skriven (för Rrk)</t>
+          <t>Godkänd baserat på raritetsblankett</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -2744,7 +2744,7 @@
         <v>119010671</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>57669</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -2744,7 +2744,7 @@
         <v>119010671</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3105,6 +3105,1173 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128284865</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98491</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>547591</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6960277</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128284869</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>547620</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6960293</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128284872</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>547627</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6960292</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128284868</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>547611</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6960291</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128280133</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>547601</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6960267</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128280081</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>547586</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6960259</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128284870</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92049</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>547621</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6960289</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128284867</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80161</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>547611</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6960292</v>
+      </c>
+      <c r="S32" t="n">
+        <v>7</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128284866</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>547611</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6960291</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128280541</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91926</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>760</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>547656</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6960341</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128280491</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Djupdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>547648</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6960333</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -3321,7 +3321,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B27" t="n">
         <v>98470</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R27" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3428,7 +3428,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B28" t="n">
         <v>98470</v>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R28" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3856,32 +3856,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128284867</v>
+        <v>128280541</v>
       </c>
       <c r="B32" t="n">
-        <v>80161</v>
+        <v>91926</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3891,13 +3891,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R32" t="n">
-        <v>6960292</v>
+        <v>6960341</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3924,19 +3924,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3951,44 +3941,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128284866</v>
+        <v>128284867</v>
       </c>
       <c r="B33" t="n">
-        <v>80132</v>
+        <v>80161</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4001,10 +3991,10 @@
         <v>547611</v>
       </c>
       <c r="R33" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4070,32 +4060,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128280541</v>
+        <v>128284866</v>
       </c>
       <c r="B34" t="n">
-        <v>91926</v>
+        <v>80132</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4105,10 +4095,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547656</v>
+        <v>547611</v>
       </c>
       <c r="R34" t="n">
-        <v>6960341</v>
+        <v>6960291</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,9 +4128,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4155,12 +4155,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -3110,7 +3110,7 @@
         <v>128284865</v>
       </c>
       <c r="B25" t="n">
-        <v>98491</v>
+        <v>98499</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>128284869</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R27" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3428,10 +3428,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B28" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R28" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3535,10 +3535,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128280133</v>
+        <v>128280081</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547601</v>
+        <v>547586</v>
       </c>
       <c r="R29" t="n">
-        <v>6960267</v>
+        <v>6960259</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128280081</v>
+        <v>128280133</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547586</v>
+        <v>547601</v>
       </c>
       <c r="R30" t="n">
-        <v>6960259</v>
+        <v>6960267</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3752,7 +3752,7 @@
         <v>128284870</v>
       </c>
       <c r="B31" t="n">
-        <v>92049</v>
+        <v>92057</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>128280541</v>
       </c>
       <c r="B32" t="n">
-        <v>91926</v>
+        <v>91934</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>128284867</v>
       </c>
       <c r="B33" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>128284866</v>
       </c>
       <c r="B34" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>128280491</v>
       </c>
       <c r="B35" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -3856,32 +3856,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128280541</v>
+        <v>128284867</v>
       </c>
       <c r="B32" t="n">
-        <v>91934</v>
+        <v>80164</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3891,13 +3891,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547656</v>
+        <v>547611</v>
       </c>
       <c r="R32" t="n">
-        <v>6960341</v>
+        <v>6960292</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3924,9 +3924,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3941,44 +3951,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128284867</v>
+        <v>128284866</v>
       </c>
       <c r="B33" t="n">
-        <v>80164</v>
+        <v>80135</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3991,10 +4001,10 @@
         <v>547611</v>
       </c>
       <c r="R33" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4060,32 +4070,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128284866</v>
+        <v>128280541</v>
       </c>
       <c r="B34" t="n">
-        <v>80135</v>
+        <v>91934</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4095,10 +4105,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R34" t="n">
-        <v>6960291</v>
+        <v>6960341</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4128,19 +4138,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4155,12 +4155,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -3110,7 +3110,7 @@
         <v>128284865</v>
       </c>
       <c r="B25" t="n">
-        <v>98499</v>
+        <v>98592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>128284869</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B27" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R27" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3428,10 +3428,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B28" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R28" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3538,7 +3538,7 @@
         <v>128280081</v>
       </c>
       <c r="B29" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>128280133</v>
       </c>
       <c r="B30" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>128284870</v>
       </c>
       <c r="B31" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3856,32 +3856,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128284867</v>
+        <v>128280541</v>
       </c>
       <c r="B32" t="n">
-        <v>80164</v>
+        <v>92026</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3891,13 +3891,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R32" t="n">
-        <v>6960292</v>
+        <v>6960341</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3924,19 +3924,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3951,44 +3941,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128284866</v>
+        <v>128284867</v>
       </c>
       <c r="B33" t="n">
-        <v>80135</v>
+        <v>80217</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4001,10 +3991,10 @@
         <v>547611</v>
       </c>
       <c r="R33" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4070,32 +4060,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128280541</v>
+        <v>128284866</v>
       </c>
       <c r="B34" t="n">
-        <v>91934</v>
+        <v>80188</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4105,10 +4095,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547656</v>
+        <v>547611</v>
       </c>
       <c r="R34" t="n">
-        <v>6960341</v>
+        <v>6960291</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,9 +4128,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4155,12 +4155,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4170,7 +4170,7 @@
         <v>128280491</v>
       </c>
       <c r="B35" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3321,7 +3321,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B27" t="n">
         <v>98571</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R27" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3428,7 +3428,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B28" t="n">
         <v>98571</v>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R28" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4272,6 +4272,103 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128622890</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92026</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>760</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>547658</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6960351</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -3321,7 +3321,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B27" t="n">
         <v>98571</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R27" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3428,7 +3428,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B28" t="n">
         <v>98571</v>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R28" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3535,7 +3535,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128280081</v>
+        <v>128280133</v>
       </c>
       <c r="B29" t="n">
         <v>57685</v>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547586</v>
+        <v>547601</v>
       </c>
       <c r="R29" t="n">
-        <v>6960259</v>
+        <v>6960267</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128280133</v>
+        <v>128280081</v>
       </c>
       <c r="B30" t="n">
         <v>57685</v>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547601</v>
+        <v>547586</v>
       </c>
       <c r="R30" t="n">
-        <v>6960267</v>
+        <v>6960259</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3856,32 +3856,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128280541</v>
+        <v>128284867</v>
       </c>
       <c r="B32" t="n">
-        <v>92026</v>
+        <v>80217</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3891,13 +3891,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547656</v>
+        <v>547611</v>
       </c>
       <c r="R32" t="n">
-        <v>6960341</v>
+        <v>6960292</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3924,9 +3924,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3941,44 +3951,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128284867</v>
+        <v>128284866</v>
       </c>
       <c r="B33" t="n">
-        <v>80217</v>
+        <v>80188</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3991,10 +4001,10 @@
         <v>547611</v>
       </c>
       <c r="R33" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4060,32 +4070,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128284866</v>
+        <v>128280541</v>
       </c>
       <c r="B34" t="n">
-        <v>80188</v>
+        <v>92026</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4095,10 +4105,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R34" t="n">
-        <v>6960291</v>
+        <v>6960341</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4128,19 +4138,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4155,12 +4155,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -4277,7 +4277,7 @@
         <v>128622890</v>
       </c>
       <c r="B36" t="n">
-        <v>92026</v>
+        <v>92032</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -3110,7 +3110,7 @@
         <v>128284865</v>
       </c>
       <c r="B25" t="n">
-        <v>98592</v>
+        <v>98606</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>128284869</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128284868</v>
       </c>
       <c r="B27" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>128284872</v>
       </c>
       <c r="B28" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128280133</v>
+        <v>128280081</v>
       </c>
       <c r="B29" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547601</v>
+        <v>547586</v>
       </c>
       <c r="R29" t="n">
-        <v>6960267</v>
+        <v>6960259</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128280081</v>
+        <v>128280133</v>
       </c>
       <c r="B30" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547586</v>
+        <v>547601</v>
       </c>
       <c r="R30" t="n">
-        <v>6960259</v>
+        <v>6960267</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3752,7 +3752,7 @@
         <v>128284870</v>
       </c>
       <c r="B31" t="n">
-        <v>92149</v>
+        <v>92161</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>128284867</v>
       </c>
       <c r="B32" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>128284866</v>
       </c>
       <c r="B33" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>128280541</v>
       </c>
       <c r="B34" t="n">
-        <v>92026</v>
+        <v>92038</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>128280491</v>
       </c>
       <c r="B35" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>128622890</v>
       </c>
       <c r="B36" t="n">
-        <v>92032</v>
+        <v>92038</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -3110,7 +3110,7 @@
         <v>128284865</v>
       </c>
       <c r="B25" t="n">
-        <v>98606</v>
+        <v>98609</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>128284869</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B27" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R27" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3428,10 +3428,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B28" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R28" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3752,7 +3752,7 @@
         <v>128284870</v>
       </c>
       <c r="B31" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3856,32 +3856,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128284867</v>
+        <v>128280541</v>
       </c>
       <c r="B32" t="n">
-        <v>80221</v>
+        <v>92040</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3891,13 +3891,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R32" t="n">
-        <v>6960292</v>
+        <v>6960341</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3924,19 +3924,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3951,12 +3941,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3966,7 +3956,7 @@
         <v>128284866</v>
       </c>
       <c r="B33" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,32 +4060,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128280541</v>
+        <v>128284867</v>
       </c>
       <c r="B34" t="n">
-        <v>92038</v>
+        <v>80223</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4105,13 +4095,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547656</v>
+        <v>547611</v>
       </c>
       <c r="R34" t="n">
-        <v>6960341</v>
+        <v>6960292</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4138,9 +4128,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4155,12 +4155,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4277,7 +4277,7 @@
         <v>128622890</v>
       </c>
       <c r="B36" t="n">
-        <v>92038</v>
+        <v>92040</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -3110,7 +3110,7 @@
         <v>128284865</v>
       </c>
       <c r="B25" t="n">
-        <v>98609</v>
+        <v>98612</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128284872</v>
       </c>
       <c r="B27" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>128284868</v>
       </c>
       <c r="B28" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3856,32 +3856,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128280541</v>
+        <v>128284867</v>
       </c>
       <c r="B32" t="n">
-        <v>92040</v>
+        <v>80223</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3891,13 +3891,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547656</v>
+        <v>547611</v>
       </c>
       <c r="R32" t="n">
-        <v>6960341</v>
+        <v>6960292</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3924,9 +3924,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3941,12 +3951,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4060,32 +4070,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128284867</v>
+        <v>128280541</v>
       </c>
       <c r="B34" t="n">
-        <v>80223</v>
+        <v>92040</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4095,13 +4105,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R34" t="n">
-        <v>6960292</v>
+        <v>6960341</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4128,19 +4138,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4155,12 +4155,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -3110,7 +3110,7 @@
         <v>128284865</v>
       </c>
       <c r="B25" t="n">
-        <v>98612</v>
+        <v>98613</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128284872</v>
       </c>
       <c r="B27" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>128284868</v>
       </c>
       <c r="B28" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>128284870</v>
       </c>
       <c r="B31" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>128280541</v>
       </c>
       <c r="B34" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>128622890</v>
       </c>
       <c r="B36" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -4277,7 +4277,7 @@
         <v>128622890</v>
       </c>
       <c r="B36" t="n">
-        <v>92041</v>
+        <v>92068</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -3110,7 +3110,7 @@
         <v>128284865</v>
       </c>
       <c r="B25" t="n">
-        <v>98613</v>
+        <v>98640</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>128284869</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B27" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R27" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3428,10 +3428,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B28" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R28" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3535,10 +3535,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128280081</v>
+        <v>128280133</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547586</v>
+        <v>547601</v>
       </c>
       <c r="R29" t="n">
-        <v>6960259</v>
+        <v>6960267</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128280133</v>
+        <v>128280081</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547601</v>
+        <v>547586</v>
       </c>
       <c r="R30" t="n">
-        <v>6960267</v>
+        <v>6960259</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3752,7 +3752,7 @@
         <v>128284870</v>
       </c>
       <c r="B31" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>128284867</v>
       </c>
       <c r="B32" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>128284866</v>
       </c>
       <c r="B33" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>128280541</v>
       </c>
       <c r="B34" t="n">
-        <v>92041</v>
+        <v>92068</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>128280491</v>
       </c>
       <c r="B35" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -3321,7 +3321,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B27" t="n">
         <v>98619</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R27" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3428,7 +3428,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B28" t="n">
         <v>98619</v>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R28" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3535,7 +3535,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128280133</v>
+        <v>128280081</v>
       </c>
       <c r="B29" t="n">
         <v>57716</v>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>547601</v>
+        <v>547586</v>
       </c>
       <c r="R29" t="n">
-        <v>6960267</v>
+        <v>6960259</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128280081</v>
+        <v>128280133</v>
       </c>
       <c r="B30" t="n">
         <v>57716</v>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>547586</v>
+        <v>547601</v>
       </c>
       <c r="R30" t="n">
-        <v>6960259</v>
+        <v>6960267</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3856,32 +3856,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128284867</v>
+        <v>128284866</v>
       </c>
       <c r="B32" t="n">
-        <v>80250</v>
+        <v>80221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3894,10 +3894,10 @@
         <v>547611</v>
       </c>
       <c r="R32" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3963,32 +3963,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128284866</v>
+        <v>128280541</v>
       </c>
       <c r="B33" t="n">
-        <v>80221</v>
+        <v>92068</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R33" t="n">
-        <v>6960291</v>
+        <v>6960341</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4031,19 +4031,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4058,44 +4048,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128280541</v>
+        <v>128284867</v>
       </c>
       <c r="B34" t="n">
-        <v>92068</v>
+        <v>80250</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4105,13 +4095,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547656</v>
+        <v>547611</v>
       </c>
       <c r="R34" t="n">
-        <v>6960341</v>
+        <v>6960292</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4138,9 +4128,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4155,12 +4155,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4277,7 +4277,7 @@
         <v>128622890</v>
       </c>
       <c r="B36" t="n">
-        <v>92068</v>
+        <v>92073</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -3110,7 +3110,7 @@
         <v>128284865</v>
       </c>
       <c r="B25" t="n">
-        <v>98640</v>
+        <v>98653</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>128284869</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>128284872</v>
       </c>
       <c r="B27" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>128284868</v>
       </c>
       <c r="B28" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>128284870</v>
       </c>
       <c r="B31" t="n">
-        <v>92191</v>
+        <v>92201</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>128284866</v>
       </c>
       <c r="B32" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3963,32 +3963,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128280541</v>
+        <v>128284867</v>
       </c>
       <c r="B33" t="n">
-        <v>92068</v>
+        <v>80254</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3998,13 +3998,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>547656</v>
+        <v>547611</v>
       </c>
       <c r="R33" t="n">
-        <v>6960341</v>
+        <v>6960292</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4031,9 +4031,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4048,44 +4058,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128284867</v>
+        <v>128280541</v>
       </c>
       <c r="B34" t="n">
-        <v>80250</v>
+        <v>92078</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4095,13 +4105,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R34" t="n">
-        <v>6960292</v>
+        <v>6960341</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4128,19 +4138,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4155,12 +4155,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4277,7 +4277,7 @@
         <v>128622890</v>
       </c>
       <c r="B36" t="n">
-        <v>92073</v>
+        <v>92078</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -3321,7 +3321,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128284872</v>
+        <v>128284868</v>
       </c>
       <c r="B27" t="n">
         <v>98632</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>547627</v>
+        <v>547611</v>
       </c>
       <c r="R27" t="n">
-        <v>6960292</v>
+        <v>6960291</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3428,7 +3428,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128284868</v>
+        <v>128284872</v>
       </c>
       <c r="B28" t="n">
         <v>98632</v>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>547611</v>
+        <v>547627</v>
       </c>
       <c r="R28" t="n">
-        <v>6960291</v>
+        <v>6960292</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3856,32 +3856,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128284866</v>
+        <v>128280541</v>
       </c>
       <c r="B32" t="n">
-        <v>80225</v>
+        <v>92078</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>547611</v>
+        <v>547656</v>
       </c>
       <c r="R32" t="n">
-        <v>6960291</v>
+        <v>6960341</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3924,19 +3924,9 @@
           <t>2025-09-07</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3951,12 +3941,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4070,32 +4060,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128280541</v>
+        <v>128284866</v>
       </c>
       <c r="B34" t="n">
-        <v>92078</v>
+        <v>80225</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4105,10 +4095,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>547656</v>
+        <v>547611</v>
       </c>
       <c r="R34" t="n">
-        <v>6960341</v>
+        <v>6960291</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4138,9 +4128,19 @@
           <t>2025-09-07</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4155,12 +4155,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -4277,7 +4277,7 @@
         <v>128622890</v>
       </c>
       <c r="B36" t="n">
-        <v>92078</v>
+        <v>92082</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -4277,7 +4277,7 @@
         <v>128622890</v>
       </c>
       <c r="B36" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -4277,7 +4277,7 @@
         <v>128622890</v>
       </c>
       <c r="B36" t="n">
-        <v>92090</v>
+        <v>92095</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 28599-2021 artfynd.xlsx
+++ b/artfynd/A 28599-2021 artfynd.xlsx
@@ -4277,7 +4277,7 @@
         <v>128622890</v>
       </c>
       <c r="B36" t="n">
-        <v>92095</v>
+        <v>92103</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
